--- a/datos2.xlsx
+++ b/datos2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/imacdevi/Documents/Work/dashboard_drink2go/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF08CF32-9090-B441-A10E-3D1892976EF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DEA1582-A2A8-9C49-A60A-8E500F0787B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="500" windowWidth="25600" windowHeight="14160" xr2:uid="{4C2A3C0A-8C4F-6843-A13D-880EAC7AAA73}"/>
+    <workbookView xWindow="34120" yWindow="500" windowWidth="17080" windowHeight="28300" xr2:uid="{4C2A3C0A-8C4F-6843-A13D-880EAC7AAA73}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="277">
   <si>
     <t>Valor de la compania</t>
   </si>
@@ -348,9 +348,6 @@
   </si>
   <si>
     <t>Ingresos totales por mercado y producto.</t>
-  </si>
-  <si>
-    <t>Total companias.Euros.</t>
   </si>
   <si>
     <t>Espana         </t>
@@ -1321,7 +1318,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6140B2E-7260-654F-97D6-EC362B30FDB3}">
-  <dimension ref="A1:M169"/>
+  <dimension ref="A1:M168"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="55.5" customWidth="1"/>
@@ -1341,7 +1338,7 @@
     </row>
     <row r="2" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -1373,7 +1370,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B4" s="5">
         <v>5.4059999999999997</v>
@@ -1392,7 +1389,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B5" s="5">
         <v>5.4630000000000001</v>
@@ -1411,7 +1408,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B6" s="5">
         <v>5.1040000000000001</v>
@@ -1430,7 +1427,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B7" s="5">
         <v>5.3440000000000003</v>
@@ -1449,7 +1446,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B8" s="5">
         <v>4.6970000000000001</v>
@@ -1468,7 +1465,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B9" s="5">
         <v>5.2030000000000003</v>
@@ -1487,7 +1484,7 @@
     </row>
     <row r="11" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A11" s="14" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
@@ -1520,7 +1517,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B13" s="8">
         <v>5.4061000000000003</v>
@@ -1543,7 +1540,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B14" s="9">
         <v>5.4627999999999997</v>
@@ -1566,7 +1563,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B15" s="9">
         <v>5.1037999999999997</v>
@@ -1589,7 +1586,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B16" s="9">
         <v>5.3444000000000003</v>
@@ -1612,7 +1609,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B17" s="9">
         <v>4.6967999999999996</v>
@@ -1740,7 +1737,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B26" s="6">
         <v>-0.09</v>
@@ -1778,7 +1775,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B28" s="6">
         <v>-0.78</v>
@@ -1854,7 +1851,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B32" s="6">
         <v>9.9</v>
@@ -1873,7 +1870,7 @@
     </row>
     <row r="33" spans="1:8" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B33" s="6">
         <v>1.2</v>
@@ -1892,7 +1889,7 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B34" s="5">
         <v>49</v>
@@ -1911,7 +1908,7 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B35" s="5">
         <v>79</v>
@@ -1930,7 +1927,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B36" s="5">
         <v>90</v>
@@ -1949,7 +1946,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B37" s="6">
         <v>4.1100000000000003</v>
@@ -2638,7 +2635,7 @@
         <v>17.363</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="111" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="8" t="s">
         <v>31</v>
       </c>
@@ -2753,7 +2750,7 @@
         <v>132.23400000000001</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="60" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="14" t="s">
         <v>40</v>
       </c>
@@ -3472,495 +3469,524 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
     </row>
-    <row r="125" spans="1:8" ht="45" x14ac:dyDescent="0.2">
-      <c r="A125" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="B125" s="15"/>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A125" s="15"/>
+      <c r="B125" s="15">
+        <v>2028</v>
+      </c>
       <c r="C125" s="15"/>
       <c r="D125" s="15"/>
-      <c r="E125" s="15"/>
+      <c r="E125" s="15">
+        <v>2027</v>
+      </c>
       <c r="F125" s="15"/>
       <c r="G125" s="15"/>
-      <c r="H125" s="15"/>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" s="15"/>
-      <c r="B126" s="15">
-        <v>2028</v>
-      </c>
-      <c r="C126" s="15"/>
-      <c r="D126" s="15"/>
-      <c r="E126" s="15">
-        <v>2027</v>
-      </c>
-      <c r="F126" s="15"/>
-      <c r="G126" s="15"/>
+      <c r="B126" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C126" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D126" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E126" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F126" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G126" s="7" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A127" s="15"/>
-      <c r="B127" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C127" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D127" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E127" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F127" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G127" s="7" t="s">
-        <v>43</v>
+      <c r="A127" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="B127" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C127" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="D127" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="E127" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="F127" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="G127" s="9" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" s="8" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B128" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="C128" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="D128" s="9" t="s">
-        <v>109</v>
+        <v>113</v>
+      </c>
+      <c r="C128" s="9">
+        <v>412.517</v>
+      </c>
+      <c r="D128" s="9">
+        <v>795.52</v>
       </c>
       <c r="E128" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="F128" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="G128" s="9" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="F128" s="9">
+        <v>398.37599999999998</v>
+      </c>
+      <c r="G128" s="9">
+        <v>859.42600000000004</v>
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A129" s="8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B129" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="C129" s="9">
-        <v>412.517</v>
-      </c>
-      <c r="D129" s="9">
-        <v>795.52</v>
+        <v>116</v>
+      </c>
+      <c r="C129" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D129" s="9" t="s">
+        <v>118</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="F129" s="9">
-        <v>398.37599999999998</v>
-      </c>
-      <c r="G129" s="9">
-        <v>859.42600000000004</v>
+        <v>119</v>
+      </c>
+      <c r="F129" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="G129" s="9" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A130" s="8" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B130" s="9" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C130" s="9" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D130" s="9" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E130" s="9" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F130" s="9" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="G130" s="9" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.2">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" ht="30" x14ac:dyDescent="0.2">
       <c r="A131" s="8" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B131" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C131" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="D131" s="9" t="s">
-        <v>126</v>
+        <v>130</v>
+      </c>
+      <c r="C131" s="9">
+        <v>960.93299999999999</v>
+      </c>
+      <c r="D131" s="9">
+        <v>531.91999999999996</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="F131" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="G131" s="9" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="132" spans="1:13" ht="30" x14ac:dyDescent="0.2">
+        <v>131</v>
+      </c>
+      <c r="F131" s="9">
+        <v>661.279</v>
+      </c>
+      <c r="G131" s="9">
+        <v>171.167</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A132" s="8" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B132" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="C132" s="9">
-        <v>960.93299999999999</v>
-      </c>
-      <c r="D132" s="9">
-        <v>531.91999999999996</v>
+        <v>133</v>
+      </c>
+      <c r="C132" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="D132" s="9" t="s">
+        <v>135</v>
       </c>
       <c r="E132" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="F132" s="9">
-        <v>661.279</v>
-      </c>
-      <c r="G132" s="9">
-        <v>171.167</v>
+        <v>136</v>
+      </c>
+      <c r="F132" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="G132" s="9" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A133" s="8" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B133" s="9" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C133" s="9" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D133" s="9" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F133" s="9" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A134" s="8" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B134" s="9" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C134" s="9" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="D134" s="9" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="E134" s="9" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="F134" s="9" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="G134" s="9" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A135" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="B135" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="C135" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="D135" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="E135" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="F135" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="G135" s="9" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A136" s="8" t="s">
+      <c r="B135" s="11">
+        <v>0.51</v>
+      </c>
+      <c r="C135" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D135" s="11">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="E135" s="11">
+        <v>0.94</v>
+      </c>
+      <c r="F135" s="11">
+        <v>0.8</v>
+      </c>
+      <c r="G135" s="11">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" ht="60" x14ac:dyDescent="0.2">
+      <c r="A138" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="B136" s="11">
-        <v>0.51</v>
-      </c>
-      <c r="C136" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="D136" s="11">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="E136" s="11">
-        <v>0.94</v>
-      </c>
-      <c r="F136" s="11">
-        <v>0.8</v>
-      </c>
-      <c r="G136" s="11">
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="139" spans="1:13" ht="60" x14ac:dyDescent="0.2">
-      <c r="A139" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="B139" s="14"/>
-      <c r="C139" s="14"/>
-      <c r="D139" s="14"/>
-      <c r="E139" s="14"/>
-      <c r="F139" s="14"/>
-      <c r="G139" s="14"/>
-      <c r="H139" s="14"/>
-      <c r="I139" s="14"/>
-      <c r="J139" s="14"/>
-      <c r="K139" s="14"/>
-      <c r="L139" s="14"/>
-      <c r="M139" s="14"/>
+      <c r="B138" s="14"/>
+      <c r="C138" s="14"/>
+      <c r="D138" s="14"/>
+      <c r="E138" s="14"/>
+      <c r="F138" s="14"/>
+      <c r="G138" s="14"/>
+      <c r="H138" s="14"/>
+      <c r="I138" s="14"/>
+      <c r="J138" s="14"/>
+      <c r="K138" s="14"/>
+      <c r="L138" s="14"/>
+      <c r="M138" s="14"/>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A139" s="15"/>
+      <c r="B139" s="15">
+        <v>2028</v>
+      </c>
+      <c r="C139" s="15"/>
+      <c r="D139" s="15">
+        <v>2027</v>
+      </c>
+      <c r="E139" s="15"/>
+      <c r="F139" s="15">
+        <v>2026</v>
+      </c>
+      <c r="G139" s="15"/>
+      <c r="H139" s="15">
+        <v>2025</v>
+      </c>
+      <c r="I139" s="15"/>
+      <c r="J139" s="15">
+        <v>2024</v>
+      </c>
+      <c r="K139" s="15"/>
+      <c r="L139" s="15">
+        <v>2023</v>
+      </c>
+      <c r="M139" s="15"/>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A140" s="15"/>
-      <c r="B140" s="15">
-        <v>2028</v>
-      </c>
-      <c r="C140" s="15"/>
-      <c r="D140" s="15">
-        <v>2027</v>
-      </c>
-      <c r="E140" s="15"/>
-      <c r="F140" s="15">
-        <v>2026</v>
-      </c>
-      <c r="G140" s="15"/>
-      <c r="H140" s="15">
-        <v>2025</v>
-      </c>
-      <c r="I140" s="15"/>
-      <c r="J140" s="15">
-        <v>2024</v>
-      </c>
-      <c r="K140" s="15"/>
-      <c r="L140" s="15">
-        <v>2023</v>
-      </c>
-      <c r="M140" s="15"/>
-    </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A141" s="15"/>
-      <c r="B141" s="7" t="s">
+      <c r="B140" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C140" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="C141" s="7" t="s">
+      <c r="D140" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="E140" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="F140" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="G140" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H140" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="I140" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="J140" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="K140" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="L140" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="M140" s="7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" ht="30" x14ac:dyDescent="0.2">
+      <c r="A141" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="D141" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="E141" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="F141" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="G141" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="H141" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="I141" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="J141" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="K141" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="L141" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="M141" s="7" t="s">
-        <v>157</v>
+      <c r="B141" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="C141" s="11">
+        <v>-1.18</v>
+      </c>
+      <c r="D141" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="E141" s="11">
+        <v>-0.15</v>
+      </c>
+      <c r="F141" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="G141" s="11">
+        <v>-1.27</v>
+      </c>
+      <c r="H141" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="I141" s="11">
+        <v>-0.15</v>
+      </c>
+      <c r="J141" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="K141" s="11">
+        <v>-2.46</v>
+      </c>
+      <c r="L141" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M141" s="11">
+        <v>0.62</v>
       </c>
     </row>
     <row r="142" spans="1:13" ht="30" x14ac:dyDescent="0.2">
       <c r="A142" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="B142" s="9" t="s">
-        <v>159</v>
+        <v>164</v>
+      </c>
+      <c r="B142" s="9">
+        <v>441.12099999999998</v>
       </c>
       <c r="C142" s="11">
-        <v>-1.18</v>
-      </c>
-      <c r="D142" s="9" t="s">
-        <v>160</v>
+        <v>1.47</v>
+      </c>
+      <c r="D142" s="9">
+        <v>384.59899999999999</v>
       </c>
       <c r="E142" s="11">
-        <v>-0.15</v>
-      </c>
-      <c r="F142" s="9" t="s">
-        <v>161</v>
+        <v>0.82</v>
+      </c>
+      <c r="F142" s="9">
+        <v>355.435</v>
       </c>
       <c r="G142" s="11">
-        <v>-1.27</v>
-      </c>
-      <c r="H142" s="9" t="s">
-        <v>162</v>
+        <v>-0.92</v>
+      </c>
+      <c r="H142" s="9">
+        <v>391.47</v>
       </c>
       <c r="I142" s="11">
-        <v>-0.15</v>
-      </c>
-      <c r="J142" s="9" t="s">
-        <v>163</v>
+        <v>-2.36</v>
+      </c>
+      <c r="J142" s="9">
+        <v>512.375</v>
       </c>
       <c r="K142" s="11">
-        <v>-2.46</v>
-      </c>
-      <c r="L142" s="9" t="s">
-        <v>164</v>
+        <v>-2.86</v>
+      </c>
+      <c r="L142" s="9">
+        <v>717.82799999999997</v>
       </c>
       <c r="M142" s="11">
-        <v>0.62</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="143" spans="1:13" ht="30" x14ac:dyDescent="0.2">
       <c r="A143" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="B143" s="9">
-        <v>441.12099999999998</v>
+      <c r="B143" s="9" t="s">
+        <v>166</v>
       </c>
       <c r="C143" s="11">
-        <v>1.47</v>
-      </c>
-      <c r="D143" s="9">
-        <v>384.59899999999999</v>
+        <v>1.08</v>
+      </c>
+      <c r="D143" s="9" t="s">
+        <v>167</v>
       </c>
       <c r="E143" s="11">
-        <v>0.82</v>
-      </c>
-      <c r="F143" s="9">
-        <v>355.435</v>
+        <v>-0.02</v>
+      </c>
+      <c r="F143" s="9" t="s">
+        <v>168</v>
       </c>
       <c r="G143" s="11">
-        <v>-0.92</v>
-      </c>
-      <c r="H143" s="9">
-        <v>391.47</v>
+        <v>-1.58</v>
+      </c>
+      <c r="H143" s="9" t="s">
+        <v>169</v>
       </c>
       <c r="I143" s="11">
-        <v>-2.36</v>
-      </c>
-      <c r="J143" s="9">
-        <v>512.375</v>
+        <v>-1.62</v>
+      </c>
+      <c r="J143" s="9" t="s">
+        <v>170</v>
       </c>
       <c r="K143" s="11">
-        <v>-2.86</v>
-      </c>
-      <c r="L143" s="9">
-        <v>717.82799999999997</v>
+        <v>-3.35</v>
+      </c>
+      <c r="L143" s="9" t="s">
+        <v>171</v>
       </c>
       <c r="M143" s="11">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="144" spans="1:13" ht="30" x14ac:dyDescent="0.2">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A144" s="8" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B144" s="9" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="C144" s="11">
-        <v>1.08</v>
+        <v>-0.98</v>
       </c>
       <c r="D144" s="9" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="E144" s="11">
-        <v>-0.02</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="F144" s="9" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="G144" s="11">
-        <v>-1.58</v>
+        <v>0.21</v>
       </c>
       <c r="H144" s="9" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="I144" s="11">
-        <v>-1.62</v>
+        <v>0.25</v>
       </c>
       <c r="J144" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="K144" s="11">
-        <v>-3.35</v>
-      </c>
-      <c r="L144" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="M144" s="11">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.2">
+        <v>177</v>
+      </c>
+      <c r="K144" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="L144" s="9">
+        <v>0</v>
+      </c>
+      <c r="M144" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" ht="30" x14ac:dyDescent="0.2">
       <c r="A145" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="B145" s="9" t="s">
-        <v>174</v>
+        <v>178</v>
+      </c>
+      <c r="B145" s="9">
+        <v>549.57500000000005</v>
       </c>
       <c r="C145" s="11">
-        <v>-0.98</v>
-      </c>
-      <c r="D145" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="E145" s="11">
-        <v>2.0499999999999998</v>
-      </c>
-      <c r="F145" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="G145" s="11">
-        <v>0.21</v>
-      </c>
-      <c r="H145" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="I145" s="11">
-        <v>0.25</v>
-      </c>
-      <c r="J145" s="9" t="s">
-        <v>178</v>
+        <v>7.95</v>
+      </c>
+      <c r="D145" s="9">
+        <v>306.12299999999999</v>
+      </c>
+      <c r="E145" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F145" s="9">
+        <v>0</v>
+      </c>
+      <c r="G145" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H145" s="9">
+        <v>0</v>
+      </c>
+      <c r="I145" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J145" s="9">
+        <v>0</v>
       </c>
       <c r="K145" s="9" t="s">
         <v>6</v>
@@ -3976,20 +4002,20 @@
       <c r="A146" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="B146" s="9">
-        <v>549.57500000000005</v>
+      <c r="B146" s="9" t="s">
+        <v>180</v>
       </c>
       <c r="C146" s="11">
-        <v>7.95</v>
-      </c>
-      <c r="D146" s="9">
-        <v>306.12299999999999</v>
-      </c>
-      <c r="E146" s="9" t="s">
-        <v>6</v>
+        <v>4.28</v>
+      </c>
+      <c r="D146" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="E146" s="11">
+        <v>4.0199999999999996</v>
       </c>
       <c r="F146" s="9">
-        <v>0</v>
+        <v>718.48400000000004</v>
       </c>
       <c r="G146" s="9" t="s">
         <v>6</v>
@@ -4015,28 +4041,28 @@
     </row>
     <row r="147" spans="1:13" ht="30" x14ac:dyDescent="0.2">
       <c r="A147" s="8" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B147" s="9" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C147" s="11">
-        <v>4.28</v>
+        <v>0.06</v>
       </c>
       <c r="D147" s="9" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E147" s="11">
-        <v>4.0199999999999996</v>
-      </c>
-      <c r="F147" s="9">
-        <v>718.48400000000004</v>
-      </c>
-      <c r="G147" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="H147" s="9">
-        <v>0</v>
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="F147" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="G147" s="11">
+        <v>3.59</v>
+      </c>
+      <c r="H147" s="9" t="s">
+        <v>186</v>
       </c>
       <c r="I147" s="9" t="s">
         <v>6</v>
@@ -4055,371 +4081,353 @@
       </c>
     </row>
     <row r="148" spans="1:13" ht="30" x14ac:dyDescent="0.2">
-      <c r="A148" s="8" t="s">
-        <v>183</v>
+      <c r="A148" s="12" t="s">
+        <v>187</v>
       </c>
       <c r="B148" s="9" t="s">
-        <v>184</v>
+        <v>11</v>
       </c>
       <c r="C148" s="11">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="D148" s="9" t="s">
-        <v>185</v>
+        <v>12</v>
       </c>
       <c r="E148" s="11">
-        <v>2.0699999999999998</v>
+        <v>1.68</v>
       </c>
       <c r="F148" s="9" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G148" s="11">
-        <v>3.59</v>
+        <v>0.75</v>
       </c>
       <c r="H148" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="I148" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="J148" s="9">
-        <v>0</v>
-      </c>
-      <c r="K148" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="L148" s="9">
-        <v>0</v>
-      </c>
-      <c r="M148" s="9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="149" spans="1:13" ht="30" x14ac:dyDescent="0.2">
-      <c r="A149" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="B149" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C149" s="11">
-        <v>0.04</v>
-      </c>
-      <c r="D149" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E149" s="11">
-        <v>1.68</v>
-      </c>
-      <c r="F149" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="G149" s="11">
-        <v>0.75</v>
-      </c>
-      <c r="H149" s="9" t="s">
+      <c r="I148" s="11">
+        <v>1.81</v>
+      </c>
+      <c r="J148" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="I149" s="11">
-        <v>1.81</v>
-      </c>
-      <c r="J149" s="9" t="s">
+      <c r="K148" s="11">
+        <v>0.03</v>
+      </c>
+      <c r="L148" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="K149" s="11">
-        <v>0.03</v>
-      </c>
-      <c r="L149" s="9" t="s">
+      <c r="M148" s="11">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" ht="60" x14ac:dyDescent="0.2">
+      <c r="A153" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="M149" s="11">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="154" spans="1:13" ht="60" x14ac:dyDescent="0.2">
-      <c r="A154" s="14" t="s">
+      <c r="B153" s="14"/>
+      <c r="C153" s="14"/>
+      <c r="D153" s="14"/>
+      <c r="E153" s="14"/>
+      <c r="F153" s="14"/>
+      <c r="G153" s="14"/>
+      <c r="H153" s="14"/>
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A154" s="15"/>
+      <c r="B154" s="7">
+        <v>2028</v>
+      </c>
+      <c r="C154" s="7">
+        <v>2027</v>
+      </c>
+      <c r="D154" s="7">
+        <v>2026</v>
+      </c>
+      <c r="E154" s="7">
+        <v>2025</v>
+      </c>
+      <c r="F154" s="7">
+        <v>2024</v>
+      </c>
+      <c r="G154" s="7">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" ht="30" x14ac:dyDescent="0.2">
+      <c r="A155" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="B154" s="14"/>
-      <c r="C154" s="14"/>
-      <c r="D154" s="14"/>
-      <c r="E154" s="14"/>
-      <c r="F154" s="14"/>
-      <c r="G154" s="14"/>
-      <c r="H154" s="14"/>
-    </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A155" s="15"/>
-      <c r="B155" s="7">
-        <v>2028</v>
-      </c>
-      <c r="C155" s="7">
-        <v>2027</v>
-      </c>
-      <c r="D155" s="7">
-        <v>2026</v>
-      </c>
-      <c r="E155" s="7">
-        <v>2025</v>
-      </c>
-      <c r="F155" s="7">
-        <v>2024</v>
-      </c>
-      <c r="G155" s="7">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="156" spans="1:13" ht="30" x14ac:dyDescent="0.2">
+      <c r="B155" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C155" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D155" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="E155" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="F155" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="G155" s="9" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" ht="45" x14ac:dyDescent="0.2">
       <c r="A156" s="8" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B156" s="9" t="s">
-        <v>15</v>
+        <v>199</v>
       </c>
       <c r="C156" s="9" t="s">
-        <v>16</v>
+        <v>200</v>
       </c>
       <c r="D156" s="9" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="E156" s="9" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="F156" s="9" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="G156" s="9" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
     <row r="157" spans="1:13" ht="45" x14ac:dyDescent="0.2">
       <c r="A157" s="8" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B157" s="9" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="C157" s="9" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="D157" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="E157" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="F157" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="G157" s="9" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="158" spans="1:13" ht="45" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="E157" s="9">
+        <v>889.55799999999999</v>
+      </c>
+      <c r="F157" s="9">
+        <v>612.30700000000002</v>
+      </c>
+      <c r="G157" s="9">
+        <v>530.81100000000004</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" ht="30" x14ac:dyDescent="0.2">
       <c r="A158" s="8" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B158" s="9" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C158" s="9" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D158" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="E158" s="9">
-        <v>889.55799999999999</v>
-      </c>
-      <c r="F158" s="9">
-        <v>612.30700000000002</v>
-      </c>
-      <c r="G158" s="9">
-        <v>530.81100000000004</v>
+        <v>212</v>
+      </c>
+      <c r="E158" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="F158" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="G158" s="9" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="159" spans="1:13" ht="30" x14ac:dyDescent="0.2">
       <c r="A159" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="B159" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="C159" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="D159" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="E159" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="F159" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="G159" s="9" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="160" spans="1:13" ht="30" x14ac:dyDescent="0.2">
+      <c r="B159" s="11">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="C159" s="11">
+        <v>8.1</v>
+      </c>
+      <c r="D159" s="11">
+        <v>8.4</v>
+      </c>
+      <c r="E159" s="11">
+        <v>8.1</v>
+      </c>
+      <c r="F159" s="11">
+        <v>7.6</v>
+      </c>
+      <c r="G159" s="11">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" ht="45" x14ac:dyDescent="0.2">
       <c r="A160" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="B160" s="11">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="C160" s="11">
-        <v>8.1</v>
-      </c>
-      <c r="D160" s="11">
-        <v>8.4</v>
-      </c>
-      <c r="E160" s="11">
-        <v>8.1</v>
-      </c>
-      <c r="F160" s="11">
-        <v>7.6</v>
-      </c>
-      <c r="G160" s="11">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" ht="45" x14ac:dyDescent="0.2">
+      <c r="B160" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="C160" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="D160" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="E160" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="F160" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="G160" s="9" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" ht="30" x14ac:dyDescent="0.2">
       <c r="A161" s="8" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B161" s="9" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C161" s="9" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="D161" s="9" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="E161" s="9" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="F161" s="9" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="G161" s="9" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" ht="45" x14ac:dyDescent="0.2">
       <c r="A162" s="8" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="B162" s="9" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="C162" s="9" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="D162" s="9" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="E162" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="F162" s="9" t="s">
-        <v>230</v>
+        <v>235</v>
+      </c>
+      <c r="F162" s="9">
+        <v>971.72</v>
       </c>
       <c r="G162" s="9" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="163" spans="1:7" ht="45" x14ac:dyDescent="0.2">
       <c r="A163" s="8" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B163" s="9" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C163" s="9" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="D163" s="9" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="E163" s="9" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="F163" s="9">
-        <v>971.72</v>
-      </c>
-      <c r="G163" s="9" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" ht="45" x14ac:dyDescent="0.2">
-      <c r="A164" s="8" t="s">
-        <v>238</v>
+        <v>990.91099999999994</v>
+      </c>
+      <c r="G163" s="9">
+        <v>760.34299999999996</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+      <c r="A164" s="13" t="s">
+        <v>242</v>
       </c>
       <c r="B164" s="9" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C164" s="9" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D164" s="9" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="E164" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="F164" s="9">
-        <v>990.91099999999994</v>
-      </c>
-      <c r="G164" s="9">
-        <v>760.34299999999996</v>
+        <v>246</v>
+      </c>
+      <c r="F164" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="G164" s="9" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="165" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A165" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="B165" s="9" t="s">
-        <v>244</v>
+      <c r="A165" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="B165" s="9">
+        <v>-188.80199999999999</v>
       </c>
       <c r="C165" s="9" t="s">
-        <v>245</v>
+        <v>18</v>
       </c>
       <c r="D165" s="9" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E165" s="9" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F165" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="G165" s="9" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+        <v>252</v>
+      </c>
+      <c r="G165" s="9">
+        <v>847.7</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" ht="45" x14ac:dyDescent="0.2">
       <c r="A166" s="8" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B166" s="9">
-        <v>-188.80199999999999</v>
-      </c>
-      <c r="C166" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D166" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="E166" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="F166" s="9" t="s">
-        <v>253</v>
+        <v>833</v>
+      </c>
+      <c r="C166" s="9">
+        <v>764</v>
+      </c>
+      <c r="D166" s="9">
+        <v>695</v>
+      </c>
+      <c r="E166" s="9">
+        <v>626</v>
+      </c>
+      <c r="F166" s="9">
+        <v>462</v>
       </c>
       <c r="G166" s="9">
-        <v>847.7</v>
+        <v>427.5</v>
       </c>
     </row>
     <row r="167" spans="1:7" ht="45" x14ac:dyDescent="0.2">
@@ -4427,71 +4435,49 @@
         <v>254</v>
       </c>
       <c r="B167" s="9">
-        <v>833</v>
+        <v>457.221</v>
       </c>
       <c r="C167" s="9">
-        <v>764</v>
+        <v>395.01499999999999</v>
       </c>
       <c r="D167" s="9">
-        <v>695</v>
+        <v>508.4</v>
       </c>
       <c r="E167" s="9">
-        <v>626</v>
+        <v>614.18899999999996</v>
       </c>
       <c r="F167" s="9">
-        <v>462</v>
+        <v>420.83800000000002</v>
       </c>
       <c r="G167" s="9">
-        <v>427.5</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" ht="45" x14ac:dyDescent="0.2">
+        <v>235.44900000000001</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" ht="30" x14ac:dyDescent="0.2">
       <c r="A168" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="B168" s="9">
-        <v>457.221</v>
-      </c>
-      <c r="C168" s="9">
-        <v>395.01499999999999</v>
-      </c>
-      <c r="D168" s="9">
-        <v>508.4</v>
-      </c>
-      <c r="E168" s="9">
-        <v>614.18899999999996</v>
-      </c>
-      <c r="F168" s="9">
-        <v>420.83800000000002</v>
+      <c r="B168" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C168" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D168" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="E168" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="F168" s="9" t="s">
+        <v>258</v>
       </c>
       <c r="G168" s="9">
-        <v>235.44900000000001</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A169" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="B169" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C169" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D169" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="E169" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="F169" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="G169" s="9">
         <v>184.751</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>